--- a/backend/data/financials_by_company/0653.HK.xlsx
+++ b/backend/data/financials_by_company/0653.HK.xlsx
@@ -662,574 +662,574 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-1193.395069</v>
+        <v>102363.707413</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00058</v>
+        <v>0.018175</v>
       </c>
       <c r="D2" t="n">
-        <v>-2057000</v>
+        <v>5632000</v>
       </c>
       <c r="E2" t="n">
-        <v>-2057000</v>
+        <v>5632000</v>
       </c>
       <c r="F2" t="n">
-        <v>-134367000</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>-216738000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>73976000</v>
+      </c>
       <c r="H2" t="n">
-        <v>47751000</v>
+        <v>577031000</v>
       </c>
       <c r="I2" t="n">
-        <v>-118888000</v>
+        <v>-102810000</v>
       </c>
       <c r="J2" t="n">
-        <v>-118888000</v>
+        <v>-176786000</v>
       </c>
       <c r="K2" t="n">
-        <v>-13348000</v>
+        <v>-41321000</v>
       </c>
       <c r="L2" t="n">
-        <v>15557000</v>
+        <v>43292000</v>
       </c>
       <c r="M2" t="n">
-        <v>2209000</v>
+        <v>1971000</v>
       </c>
       <c r="N2" t="n">
-        <v>-132311193.395069</v>
+        <v>-222267636.292587</v>
       </c>
       <c r="O2" t="n">
-        <v>-134367000</v>
+        <v>-216738000</v>
       </c>
       <c r="P2" t="n">
-        <v>135752000</v>
+        <v>848163000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-51945000</v>
+        <v>-176786000</v>
       </c>
       <c r="R2" t="n">
-        <v>237715799</v>
+        <v>216226460</v>
       </c>
       <c r="S2" t="n">
-        <v>237715799</v>
+        <v>173080354</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.26</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.26</v>
       </c>
       <c r="V2" t="n">
-        <v>-134367000</v>
+        <v>-216738000</v>
       </c>
       <c r="W2" t="n">
-        <v>-134367000</v>
+        <v>-216738000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-134367000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>-216738000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-660000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>-134367000</v>
+        <v>-216078000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-134367000</v>
+        <v>-216078000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-78000</v>
+        <v>-4000000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-134445000</v>
+        <v>-220078000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2697000</v>
+        <v>36783000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2057000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>5632000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-35945000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>2057000</v>
+        <v>12574000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>17739000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-13348000</v>
+        <v>-41321000</v>
       </c>
       <c r="AK2" t="n">
-        <v>15557000</v>
+        <v>43292000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2209000</v>
+        <v>1971000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-55206000</v>
+        <v>-221172000</v>
       </c>
       <c r="AN2" t="n">
-        <v>88001000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>271132000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>965000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>88062000</v>
+        <v>270167000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5454000</v>
+        <v>16681000</v>
       </c>
       <c r="AR2" t="n">
-        <v>82608000</v>
+        <v>253486000</v>
       </c>
       <c r="AS2" t="n">
-        <v>32795000</v>
+        <v>49960000</v>
       </c>
       <c r="AT2" t="n">
-        <v>47751000</v>
+        <v>577031000</v>
       </c>
       <c r="AU2" t="n">
-        <v>80546000</v>
+        <v>626991000</v>
       </c>
       <c r="AV2" t="n">
-        <v>80546000</v>
+        <v>626991000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1192574.389775</v>
+        <v>56353770</v>
       </c>
       <c r="C3" t="n">
-        <v>0.011719</v>
+        <v>0.165</v>
       </c>
       <c r="D3" t="n">
-        <v>101762000</v>
+        <v>341538000</v>
       </c>
       <c r="E3" t="n">
-        <v>101762000</v>
+        <v>341538000</v>
       </c>
       <c r="F3" t="n">
-        <v>53971000</v>
+        <v>167221000</v>
       </c>
       <c r="G3" t="n">
-        <v>23643000</v>
+        <v>27615000</v>
       </c>
       <c r="H3" t="n">
-        <v>887219000</v>
+        <v>151908000</v>
       </c>
       <c r="I3" t="n">
-        <v>91635000</v>
+        <v>226728000</v>
       </c>
       <c r="J3" t="n">
-        <v>67992000</v>
+        <v>199113000</v>
       </c>
       <c r="K3" t="n">
-        <v>-9280000</v>
+        <v>-33610000</v>
       </c>
       <c r="L3" t="n">
-        <v>13381000</v>
+        <v>34624000</v>
       </c>
       <c r="M3" t="n">
-        <v>4101000</v>
+        <v>1014000</v>
       </c>
       <c r="N3" t="n">
-        <v>-46598425.610225</v>
+        <v>-117963230</v>
       </c>
       <c r="O3" t="n">
-        <v>53971000</v>
+        <v>167221000</v>
       </c>
       <c r="P3" t="n">
-        <v>1013710000</v>
+        <v>322488000</v>
       </c>
       <c r="Q3" t="n">
-        <v>43217000</v>
+        <v>199113000</v>
       </c>
       <c r="R3" t="n">
-        <v>231309934</v>
+        <v>219409566</v>
       </c>
       <c r="S3" t="n">
-        <v>231309934</v>
+        <v>175628299</v>
       </c>
       <c r="T3" t="n">
-        <v>0.240138</v>
+        <v>0.96</v>
       </c>
       <c r="U3" t="n">
-        <v>0.240138</v>
+        <v>0.96</v>
       </c>
       <c r="V3" t="n">
-        <v>53971000</v>
+        <v>167221000</v>
       </c>
       <c r="W3" t="n">
-        <v>53971000</v>
+        <v>167221000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>53971000</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
+        <v>167221000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
       <c r="AA3" t="n">
-        <v>53971000</v>
+        <v>167221000</v>
       </c>
       <c r="AB3" t="n">
-        <v>53971000</v>
+        <v>167221000</v>
       </c>
       <c r="AC3" t="n">
-        <v>640000</v>
+        <v>-2732000</v>
       </c>
       <c r="AD3" t="n">
-        <v>54611000</v>
+        <v>164489000</v>
       </c>
       <c r="AE3" t="n">
-        <v>638000</v>
+        <v>1174000</v>
       </c>
       <c r="AF3" t="n">
-        <v>101762000</v>
+        <v>341538000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-102996000</v>
+        <v>-354633000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1072000</v>
+        <v>11246000</v>
       </c>
       <c r="AI3" t="n">
-        <v>162000</v>
+        <v>1849000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-9280000</v>
+        <v>-33610000</v>
       </c>
       <c r="AK3" t="n">
-        <v>13381000</v>
+        <v>34624000</v>
       </c>
       <c r="AL3" t="n">
-        <v>4101000</v>
+        <v>1014000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-63439000</v>
+        <v>-136826000</v>
       </c>
       <c r="AN3" t="n">
-        <v>126491000</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>170580000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>125000</v>
+      </c>
       <c r="AP3" t="n">
-        <v>131225000</v>
+        <v>171010000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15166000</v>
+        <v>16369000</v>
       </c>
       <c r="AR3" t="n">
-        <v>116059000</v>
+        <v>154641000</v>
       </c>
       <c r="AS3" t="n">
-        <v>63052000</v>
+        <v>33754000</v>
       </c>
       <c r="AT3" t="n">
-        <v>887219000</v>
+        <v>151908000</v>
       </c>
       <c r="AU3" t="n">
-        <v>950271000</v>
+        <v>185662000</v>
       </c>
       <c r="AV3" t="n">
-        <v>950271000</v>
+        <v>185662000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>56353770</v>
+        <v>1192574.389775</v>
       </c>
       <c r="C4" t="n">
-        <v>0.165</v>
+        <v>0.011719</v>
       </c>
       <c r="D4" t="n">
-        <v>341538000</v>
+        <v>101762000</v>
       </c>
       <c r="E4" t="n">
-        <v>341538000</v>
+        <v>101762000</v>
       </c>
       <c r="F4" t="n">
-        <v>167221000</v>
+        <v>53971000</v>
       </c>
       <c r="G4" t="n">
-        <v>27615000</v>
+        <v>23643000</v>
       </c>
       <c r="H4" t="n">
-        <v>151908000</v>
+        <v>887219000</v>
       </c>
       <c r="I4" t="n">
-        <v>226728000</v>
+        <v>91635000</v>
       </c>
       <c r="J4" t="n">
-        <v>199113000</v>
+        <v>67992000</v>
       </c>
       <c r="K4" t="n">
-        <v>-33610000</v>
+        <v>-9280000</v>
       </c>
       <c r="L4" t="n">
-        <v>34624000</v>
+        <v>13381000</v>
       </c>
       <c r="M4" t="n">
-        <v>1014000</v>
+        <v>4101000</v>
       </c>
       <c r="N4" t="n">
-        <v>-117963230</v>
+        <v>-46598425.610225</v>
       </c>
       <c r="O4" t="n">
-        <v>167221000</v>
+        <v>53971000</v>
       </c>
       <c r="P4" t="n">
-        <v>322488000</v>
+        <v>1013710000</v>
       </c>
       <c r="Q4" t="n">
-        <v>199113000</v>
+        <v>43217000</v>
       </c>
       <c r="R4" t="n">
-        <v>219409566</v>
+        <v>231309934</v>
       </c>
       <c r="S4" t="n">
-        <v>175628299</v>
+        <v>231309934</v>
       </c>
       <c r="T4" t="n">
-        <v>0.96</v>
+        <v>0.240138</v>
       </c>
       <c r="U4" t="n">
-        <v>0.96</v>
+        <v>0.240138</v>
       </c>
       <c r="V4" t="n">
-        <v>167221000</v>
+        <v>53971000</v>
       </c>
       <c r="W4" t="n">
-        <v>167221000</v>
+        <v>53971000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>167221000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
+        <v>53971000</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>167221000</v>
+        <v>53971000</v>
       </c>
       <c r="AB4" t="n">
-        <v>167221000</v>
+        <v>53971000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2732000</v>
+        <v>640000</v>
       </c>
       <c r="AD4" t="n">
-        <v>164489000</v>
+        <v>54611000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1174000</v>
+        <v>638000</v>
       </c>
       <c r="AF4" t="n">
-        <v>341538000</v>
+        <v>101762000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-354633000</v>
+        <v>-102996000</v>
       </c>
       <c r="AH4" t="n">
-        <v>11246000</v>
+        <v>1072000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1849000</v>
+        <v>162000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-33610000</v>
+        <v>-9280000</v>
       </c>
       <c r="AK4" t="n">
-        <v>34624000</v>
+        <v>13381000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1014000</v>
+        <v>4101000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-136826000</v>
+        <v>-63439000</v>
       </c>
       <c r="AN4" t="n">
-        <v>170580000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>125000</v>
-      </c>
+        <v>126491000</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>171010000</v>
+        <v>131225000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16369000</v>
+        <v>15166000</v>
       </c>
       <c r="AR4" t="n">
-        <v>154641000</v>
+        <v>116059000</v>
       </c>
       <c r="AS4" t="n">
-        <v>33754000</v>
+        <v>63052000</v>
       </c>
       <c r="AT4" t="n">
-        <v>151908000</v>
+        <v>887219000</v>
       </c>
       <c r="AU4" t="n">
-        <v>185662000</v>
+        <v>950271000</v>
       </c>
       <c r="AV4" t="n">
-        <v>185662000</v>
+        <v>950271000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>102363.707413</v>
+        <v>-1193.395069</v>
       </c>
       <c r="C5" t="n">
-        <v>0.018175</v>
+        <v>0.00058</v>
       </c>
       <c r="D5" t="n">
-        <v>5632000</v>
+        <v>-2057000</v>
       </c>
       <c r="E5" t="n">
-        <v>5632000</v>
+        <v>-2057000</v>
       </c>
       <c r="F5" t="n">
-        <v>-216738000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>73976000</v>
-      </c>
+        <v>-134367000</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>577031000</v>
+        <v>47751000</v>
       </c>
       <c r="I5" t="n">
-        <v>-102810000</v>
+        <v>-118888000</v>
       </c>
       <c r="J5" t="n">
-        <v>-176786000</v>
+        <v>-118888000</v>
       </c>
       <c r="K5" t="n">
-        <v>-41321000</v>
+        <v>-13348000</v>
       </c>
       <c r="L5" t="n">
-        <v>43292000</v>
+        <v>15557000</v>
       </c>
       <c r="M5" t="n">
-        <v>1971000</v>
+        <v>2209000</v>
       </c>
       <c r="N5" t="n">
-        <v>-222267636.292587</v>
+        <v>-132311193.395069</v>
       </c>
       <c r="O5" t="n">
-        <v>-216738000</v>
+        <v>-134367000</v>
       </c>
       <c r="P5" t="n">
-        <v>848163000</v>
+        <v>135752000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-176786000</v>
+        <v>-51945000</v>
       </c>
       <c r="R5" t="n">
-        <v>216226460</v>
+        <v>237715799</v>
       </c>
       <c r="S5" t="n">
-        <v>173080354</v>
+        <v>237715799</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.26</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.26</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-216738000</v>
+        <v>-134367000</v>
       </c>
       <c r="W5" t="n">
-        <v>-216738000</v>
+        <v>-134367000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-216738000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-660000</v>
-      </c>
+        <v>-134367000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>-216078000</v>
+        <v>-134367000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-216078000</v>
+        <v>-134367000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4000000</v>
+        <v>-78000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-220078000</v>
+        <v>-134445000</v>
       </c>
       <c r="AE5" t="n">
-        <v>36783000</v>
+        <v>2697000</v>
       </c>
       <c r="AF5" t="n">
-        <v>5632000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-35945000</v>
-      </c>
+        <v>-2057000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>12574000</v>
+        <v>2057000</v>
       </c>
       <c r="AI5" t="n">
-        <v>17739000</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-41321000</v>
+        <v>-13348000</v>
       </c>
       <c r="AK5" t="n">
-        <v>43292000</v>
+        <v>15557000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1971000</v>
+        <v>2209000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-221172000</v>
+        <v>-55206000</v>
       </c>
       <c r="AN5" t="n">
-        <v>271132000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>965000</v>
-      </c>
+        <v>88001000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>270167000</v>
+        <v>88062000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16681000</v>
+        <v>5454000</v>
       </c>
       <c r="AR5" t="n">
-        <v>253486000</v>
+        <v>82608000</v>
       </c>
       <c r="AS5" t="n">
-        <v>49960000</v>
+        <v>32795000</v>
       </c>
       <c r="AT5" t="n">
-        <v>577031000</v>
+        <v>47751000</v>
       </c>
       <c r="AU5" t="n">
-        <v>626991000</v>
+        <v>80546000</v>
       </c>
       <c r="AV5" t="n">
-        <v>626991000</v>
+        <v>80546000</v>
       </c>
     </row>
   </sheetData>
@@ -1590,308 +1590,342 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>237715799</v>
+        <v>175628299</v>
       </c>
       <c r="C2" t="n">
-        <v>237715799</v>
+        <v>175628299</v>
       </c>
       <c r="D2" t="n">
-        <v>57585000</v>
+        <v>155654000</v>
       </c>
       <c r="E2" t="n">
-        <v>127829000</v>
+        <v>225469000</v>
       </c>
       <c r="F2" t="n">
-        <v>148654000</v>
+        <v>2787000</v>
       </c>
       <c r="G2" t="n">
-        <v>212687000</v>
+        <v>200275000</v>
       </c>
       <c r="H2" t="n">
-        <v>-133906000</v>
+        <v>-55339000</v>
       </c>
       <c r="I2" t="n">
-        <v>148654000</v>
+        <v>2787000</v>
       </c>
       <c r="J2" t="n">
-        <v>63796000</v>
+        <v>27981000</v>
       </c>
       <c r="K2" t="n">
-        <v>148654000</v>
+        <v>2787000</v>
       </c>
       <c r="L2" t="n">
-        <v>179989000</v>
+        <v>28762000</v>
       </c>
       <c r="M2" t="n">
-        <v>148654000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>2787000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
       <c r="O2" t="n">
-        <v>148654000</v>
+        <v>2787000</v>
       </c>
       <c r="P2" t="n">
-        <v>22037000</v>
+        <v>23428000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-168382000</v>
+        <v>-277069000</v>
       </c>
       <c r="R2" t="n">
-        <v>293654000</v>
+        <v>229083000</v>
       </c>
       <c r="S2" t="n">
-        <v>2377000</v>
+        <v>35126000</v>
       </c>
       <c r="T2" t="n">
-        <v>2377000</v>
+        <v>35126000</v>
       </c>
       <c r="U2" t="n">
-        <v>273040000</v>
+        <v>696256000</v>
       </c>
       <c r="V2" t="n">
-        <v>46902000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>34102000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1296000</v>
+      </c>
       <c r="X2" t="n">
-        <v>1153000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>1296000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" t="n">
-        <v>45749000</v>
+        <v>32806000</v>
       </c>
       <c r="AA2" t="n">
-        <v>14414000</v>
+        <v>6831000</v>
       </c>
       <c r="AB2" t="n">
-        <v>31335000</v>
+        <v>25975000</v>
       </c>
       <c r="AC2" t="n">
-        <v>226138000</v>
+        <v>662154000</v>
       </c>
       <c r="AD2" t="n">
-        <v>82080000</v>
+        <v>192663000</v>
       </c>
       <c r="AE2" t="n">
-        <v>49382000</v>
+        <v>21150000</v>
       </c>
       <c r="AF2" t="n">
-        <v>32698000</v>
+        <v>171513000</v>
       </c>
       <c r="AG2" t="n">
-        <v>138980000</v>
+        <v>58958000</v>
       </c>
       <c r="AH2" t="n">
-        <v>133805000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>40182000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>2732000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>5175000</v>
+        <v>16044000</v>
       </c>
       <c r="AK2" t="n">
-        <v>421694000</v>
+        <v>699043000</v>
       </c>
       <c r="AL2" t="n">
-        <v>329462000</v>
+        <v>92228000</v>
       </c>
       <c r="AM2" t="n">
-        <v>4858000</v>
+        <v>5129000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>71172000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>71172000</v>
+      </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>302008000</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>301457000</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>551000</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
       <c r="AV2" t="n">
-        <v>22596000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>15927000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-158753000</v>
+      </c>
       <c r="AX2" t="n">
-        <v>22596000</v>
+        <v>174680000</v>
       </c>
       <c r="AY2" t="n">
-        <v>22596000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
+        <v>13673000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>68410000</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>90298000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>2299000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
       <c r="BD2" t="n">
-        <v>92232000</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>606815000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>498454000</v>
+      </c>
       <c r="BF2" t="n">
-        <v>1028000</v>
+        <v>31848000</v>
       </c>
       <c r="BG2" t="n">
-        <v>4011000</v>
-      </c>
-      <c r="BH2" t="inlineStr"/>
+        <v>26373000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>26373000</v>
+      </c>
       <c r="BI2" t="n">
-        <v>60058000</v>
+        <v>4224000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>20687000</v>
+        <v>4082000</v>
       </c>
       <c r="BK2" t="n">
-        <v>-2113000</v>
+        <v>-2500000</v>
       </c>
       <c r="BL2" t="n">
-        <v>22800000</v>
+        <v>6582000</v>
       </c>
       <c r="BM2" t="n">
-        <v>6448000</v>
+        <v>41834000</v>
       </c>
       <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="n">
-        <v>6448000</v>
-      </c>
-      <c r="BP2" t="inlineStr"/>
+        <v>41834000</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>200000</v>
+      </c>
       <c r="BQ2" t="n">
-        <v>6448000</v>
+        <v>41634000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>237715799</v>
+        <v>175628300</v>
       </c>
       <c r="C3" t="n">
-        <v>237715799</v>
+        <v>175628300</v>
       </c>
       <c r="D3" t="n">
-        <v>31404000</v>
+        <v>23834000</v>
       </c>
       <c r="E3" t="n">
-        <v>116508000</v>
+        <v>138291000</v>
       </c>
       <c r="F3" t="n">
-        <v>282236000</v>
+        <v>155388000</v>
       </c>
       <c r="G3" t="n">
-        <v>329749000</v>
+        <v>197151000</v>
       </c>
       <c r="H3" t="n">
-        <v>-52994000</v>
+        <v>-169740000</v>
       </c>
       <c r="I3" t="n">
-        <v>282236000</v>
+        <v>155388000</v>
       </c>
       <c r="J3" t="n">
-        <v>68995000</v>
+        <v>96528000</v>
       </c>
       <c r="K3" t="n">
-        <v>282236000</v>
+        <v>155388000</v>
       </c>
       <c r="L3" t="n">
-        <v>314415000</v>
+        <v>175054000</v>
       </c>
       <c r="M3" t="n">
-        <v>282236000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>155388000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
       <c r="O3" t="n">
-        <v>282236000</v>
+        <v>155388000</v>
       </c>
       <c r="P3" t="n">
         <v>22037000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-79251000</v>
+        <v>-122647000</v>
       </c>
       <c r="R3" t="n">
-        <v>293654000</v>
+        <v>229083000</v>
       </c>
       <c r="S3" t="n">
-        <v>47543000</v>
+        <v>35126000</v>
       </c>
       <c r="T3" t="n">
-        <v>47543000</v>
+        <v>35126000</v>
       </c>
       <c r="U3" t="n">
-        <v>221872000</v>
+        <v>350019000</v>
       </c>
       <c r="V3" t="n">
-        <v>74503000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>85910000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1039000</v>
+      </c>
       <c r="X3" t="n">
-        <v>1239000</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+        <v>1039000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
       <c r="Z3" t="n">
-        <v>73264000</v>
+        <v>84871000</v>
       </c>
       <c r="AA3" t="n">
-        <v>41085000</v>
+        <v>65205000</v>
       </c>
       <c r="AB3" t="n">
-        <v>32179000</v>
+        <v>19666000</v>
       </c>
       <c r="AC3" t="n">
-        <v>147369000</v>
+        <v>264109000</v>
       </c>
       <c r="AD3" t="n">
-        <v>43244000</v>
+        <v>53420000</v>
       </c>
       <c r="AE3" t="n">
-        <v>27910000</v>
+        <v>31323000</v>
       </c>
       <c r="AF3" t="n">
-        <v>15334000</v>
+        <v>22097000</v>
       </c>
       <c r="AG3" t="n">
-        <v>36953000</v>
+        <v>86255000</v>
       </c>
       <c r="AH3" t="n">
-        <v>32142000</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>68890000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>4811000</v>
+        <v>17365000</v>
       </c>
       <c r="AK3" t="n">
-        <v>504108000</v>
+        <v>505407000</v>
       </c>
       <c r="AL3" t="n">
-        <v>409733000</v>
+        <v>411038000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1991000</v>
+        <v>7401000</v>
       </c>
       <c r="AN3" t="n">
-        <v>409000</v>
+        <v>349000</v>
       </c>
       <c r="AO3" t="n">
-        <v>409000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
+        <v>349000</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>368951000</v>
+        <v>343625000</v>
       </c>
       <c r="AR3" t="n">
-        <v>368400000</v>
+        <v>343625000</v>
       </c>
       <c r="AS3" t="n">
-        <v>551000</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
@@ -1900,20 +1934,22 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>38382000</v>
+        <v>54763000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-15956000</v>
+        <v>-23068000</v>
       </c>
       <c r="AX3" t="n">
-        <v>54338000</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+        <v>77831000</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>54763000</v>
+      </c>
       <c r="AZ3" t="n">
-        <v>7197000</v>
+        <v>13467000</v>
       </c>
       <c r="BA3" t="n">
-        <v>47141000</v>
+        <v>64364000</v>
       </c>
       <c r="BB3" t="n">
         <v>0</v>
@@ -1922,175 +1958,175 @@
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>94375000</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
+        <v>94369000</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
       <c r="BF3" t="n">
-        <v>31052000</v>
+        <v>25926000</v>
       </c>
       <c r="BG3" t="n">
-        <v>9657000</v>
+        <v>7127000</v>
       </c>
       <c r="BH3" t="n">
-        <v>9657000</v>
+        <v>7127000</v>
       </c>
       <c r="BI3" t="n">
-        <v>36397000</v>
+        <v>18589000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1160000</v>
+        <v>777000</v>
       </c>
       <c r="BK3" t="n">
-        <v>-843000</v>
+        <v>-6125000</v>
       </c>
       <c r="BL3" t="n">
-        <v>2003000</v>
+        <v>6902000</v>
       </c>
       <c r="BM3" t="n">
-        <v>16109000</v>
-      </c>
-      <c r="BN3" t="inlineStr"/>
+        <v>41950000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>24021000</v>
+      </c>
       <c r="BO3" t="n">
-        <v>16109000</v>
-      </c>
-      <c r="BP3" t="inlineStr"/>
+        <v>17929000</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0</v>
+      </c>
       <c r="BQ3" t="n">
-        <v>16109000</v>
+        <v>17929000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>175628300</v>
+        <v>237715799</v>
       </c>
       <c r="C4" t="n">
-        <v>175628300</v>
+        <v>237715799</v>
       </c>
       <c r="D4" t="n">
-        <v>23834000</v>
+        <v>31404000</v>
       </c>
       <c r="E4" t="n">
-        <v>138291000</v>
+        <v>116508000</v>
       </c>
       <c r="F4" t="n">
-        <v>155388000</v>
+        <v>282236000</v>
       </c>
       <c r="G4" t="n">
-        <v>197151000</v>
+        <v>329749000</v>
       </c>
       <c r="H4" t="n">
-        <v>-169740000</v>
+        <v>-52994000</v>
       </c>
       <c r="I4" t="n">
-        <v>155388000</v>
+        <v>282236000</v>
       </c>
       <c r="J4" t="n">
-        <v>96528000</v>
+        <v>68995000</v>
       </c>
       <c r="K4" t="n">
-        <v>155388000</v>
+        <v>282236000</v>
       </c>
       <c r="L4" t="n">
-        <v>175054000</v>
+        <v>314415000</v>
       </c>
       <c r="M4" t="n">
-        <v>155388000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+        <v>282236000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>155388000</v>
+        <v>282236000</v>
       </c>
       <c r="P4" t="n">
         <v>22037000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-122647000</v>
+        <v>-79251000</v>
       </c>
       <c r="R4" t="n">
-        <v>229083000</v>
+        <v>293654000</v>
       </c>
       <c r="S4" t="n">
-        <v>35126000</v>
+        <v>47543000</v>
       </c>
       <c r="T4" t="n">
-        <v>35126000</v>
+        <v>47543000</v>
       </c>
       <c r="U4" t="n">
-        <v>350019000</v>
+        <v>221872000</v>
       </c>
       <c r="V4" t="n">
-        <v>85910000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1039000</v>
-      </c>
+        <v>74503000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>1039000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
+        <v>1239000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>84871000</v>
+        <v>73264000</v>
       </c>
       <c r="AA4" t="n">
-        <v>65205000</v>
+        <v>41085000</v>
       </c>
       <c r="AB4" t="n">
-        <v>19666000</v>
+        <v>32179000</v>
       </c>
       <c r="AC4" t="n">
-        <v>264109000</v>
+        <v>147369000</v>
       </c>
       <c r="AD4" t="n">
-        <v>53420000</v>
+        <v>43244000</v>
       </c>
       <c r="AE4" t="n">
-        <v>31323000</v>
+        <v>27910000</v>
       </c>
       <c r="AF4" t="n">
-        <v>22097000</v>
+        <v>15334000</v>
       </c>
       <c r="AG4" t="n">
-        <v>86255000</v>
+        <v>36953000</v>
       </c>
       <c r="AH4" t="n">
-        <v>68890000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
+        <v>32142000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>17365000</v>
+        <v>4811000</v>
       </c>
       <c r="AK4" t="n">
-        <v>505407000</v>
+        <v>504108000</v>
       </c>
       <c r="AL4" t="n">
-        <v>411038000</v>
+        <v>409733000</v>
       </c>
       <c r="AM4" t="n">
-        <v>7401000</v>
+        <v>1991000</v>
       </c>
       <c r="AN4" t="n">
-        <v>349000</v>
+        <v>409000</v>
       </c>
       <c r="AO4" t="n">
-        <v>349000</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>409000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>343625000</v>
+        <v>368951000</v>
       </c>
       <c r="AR4" t="n">
-        <v>343625000</v>
+        <v>368400000</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>551000</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
@@ -2099,22 +2135,20 @@
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>54763000</v>
+        <v>38382000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-23068000</v>
+        <v>-15956000</v>
       </c>
       <c r="AX4" t="n">
-        <v>77831000</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>54763000</v>
-      </c>
+        <v>54338000</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>13467000</v>
+        <v>7197000</v>
       </c>
       <c r="BA4" t="n">
-        <v>64364000</v>
+        <v>47141000</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
@@ -2123,251 +2157,217 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>94369000</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
+        <v>94375000</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>25926000</v>
+        <v>31052000</v>
       </c>
       <c r="BG4" t="n">
-        <v>7127000</v>
+        <v>9657000</v>
       </c>
       <c r="BH4" t="n">
-        <v>7127000</v>
+        <v>9657000</v>
       </c>
       <c r="BI4" t="n">
-        <v>18589000</v>
+        <v>36397000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>777000</v>
+        <v>1160000</v>
       </c>
       <c r="BK4" t="n">
-        <v>-6125000</v>
+        <v>-843000</v>
       </c>
       <c r="BL4" t="n">
-        <v>6902000</v>
+        <v>2003000</v>
       </c>
       <c r="BM4" t="n">
-        <v>41950000</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>24021000</v>
-      </c>
+        <v>16109000</v>
+      </c>
+      <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="n">
-        <v>17929000</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
+        <v>16109000</v>
+      </c>
+      <c r="BP4" t="inlineStr"/>
       <c r="BQ4" t="n">
-        <v>17929000</v>
+        <v>16109000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>175628299</v>
+        <v>237715799</v>
       </c>
       <c r="C5" t="n">
-        <v>175628299</v>
+        <v>237715799</v>
       </c>
       <c r="D5" t="n">
-        <v>155654000</v>
+        <v>57585000</v>
       </c>
       <c r="E5" t="n">
-        <v>225469000</v>
+        <v>127829000</v>
       </c>
       <c r="F5" t="n">
-        <v>2787000</v>
+        <v>148654000</v>
       </c>
       <c r="G5" t="n">
-        <v>200275000</v>
+        <v>212687000</v>
       </c>
       <c r="H5" t="n">
-        <v>-55339000</v>
+        <v>-133906000</v>
       </c>
       <c r="I5" t="n">
-        <v>2787000</v>
+        <v>148654000</v>
       </c>
       <c r="J5" t="n">
-        <v>27981000</v>
+        <v>63796000</v>
       </c>
       <c r="K5" t="n">
-        <v>2787000</v>
+        <v>148654000</v>
       </c>
       <c r="L5" t="n">
-        <v>28762000</v>
+        <v>179989000</v>
       </c>
       <c r="M5" t="n">
-        <v>2787000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+        <v>148654000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>2787000</v>
+        <v>148654000</v>
       </c>
       <c r="P5" t="n">
-        <v>23428000</v>
+        <v>22037000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-277069000</v>
+        <v>-168382000</v>
       </c>
       <c r="R5" t="n">
-        <v>229083000</v>
+        <v>293654000</v>
       </c>
       <c r="S5" t="n">
-        <v>35126000</v>
+        <v>2377000</v>
       </c>
       <c r="T5" t="n">
-        <v>35126000</v>
+        <v>2377000</v>
       </c>
       <c r="U5" t="n">
-        <v>696256000</v>
+        <v>273040000</v>
       </c>
       <c r="V5" t="n">
-        <v>34102000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1296000</v>
-      </c>
+        <v>46902000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>1296000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
+        <v>1153000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>32806000</v>
+        <v>45749000</v>
       </c>
       <c r="AA5" t="n">
-        <v>6831000</v>
+        <v>14414000</v>
       </c>
       <c r="AB5" t="n">
-        <v>25975000</v>
+        <v>31335000</v>
       </c>
       <c r="AC5" t="n">
-        <v>662154000</v>
+        <v>226138000</v>
       </c>
       <c r="AD5" t="n">
-        <v>192663000</v>
+        <v>82080000</v>
       </c>
       <c r="AE5" t="n">
-        <v>21150000</v>
+        <v>49382000</v>
       </c>
       <c r="AF5" t="n">
-        <v>171513000</v>
+        <v>32698000</v>
       </c>
       <c r="AG5" t="n">
-        <v>58958000</v>
+        <v>138980000</v>
       </c>
       <c r="AH5" t="n">
-        <v>40182000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>2732000</v>
-      </c>
+        <v>133805000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>16044000</v>
+        <v>5175000</v>
       </c>
       <c r="AK5" t="n">
-        <v>699043000</v>
+        <v>421694000</v>
       </c>
       <c r="AL5" t="n">
-        <v>92228000</v>
+        <v>329462000</v>
       </c>
       <c r="AM5" t="n">
-        <v>5129000</v>
+        <v>4858000</v>
       </c>
       <c r="AN5" t="n">
-        <v>71172000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>71172000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>302008000</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>301457000</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>551000</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>15927000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-158753000</v>
-      </c>
+        <v>22596000</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>174680000</v>
+        <v>22596000</v>
       </c>
       <c r="AY5" t="n">
-        <v>13673000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>68410000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>90298000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2299000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
+        <v>22596000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>606815000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>498454000</v>
-      </c>
+        <v>92232000</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>31848000</v>
+        <v>1028000</v>
       </c>
       <c r="BG5" t="n">
-        <v>26373000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>26373000</v>
-      </c>
+        <v>4011000</v>
+      </c>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="n">
-        <v>4224000</v>
+        <v>60058000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>4082000</v>
+        <v>20687000</v>
       </c>
       <c r="BK5" t="n">
-        <v>-2500000</v>
+        <v>-2113000</v>
       </c>
       <c r="BL5" t="n">
-        <v>6582000</v>
+        <v>22800000</v>
       </c>
       <c r="BM5" t="n">
-        <v>41834000</v>
+        <v>6448000</v>
       </c>
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="n">
-        <v>41834000</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>200000</v>
-      </c>
+        <v>6448000</v>
+      </c>
+      <c r="BP5" t="inlineStr"/>
       <c r="BQ5" t="n">
-        <v>41634000</v>
+        <v>6448000</v>
       </c>
     </row>
   </sheetData>
@@ -2638,511 +2638,511 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-64787000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+        <v>-108417000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-92066000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>161857000</v>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>6448000</v>
+        <v>41947000</v>
       </c>
       <c r="G2" t="n">
-        <v>16109000</v>
+        <v>16748000</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-733000</v>
       </c>
       <c r="I2" t="n">
-        <v>-9661000</v>
+        <v>25932000</v>
       </c>
       <c r="J2" t="n">
-        <v>56619000</v>
+        <v>-10132000</v>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>69791000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-38772000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-38772000</v>
+      </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>69791000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-92066000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>161857000</v>
+      </c>
       <c r="S2" t="n">
-        <v>-1493000</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+        <v>144481000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>19723000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>11641000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>11641000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>113107000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>113107000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
       <c r="AG2" t="n">
-        <v>-64787000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+        <v>-108417000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>210000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-35047000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>40240000</v>
+      </c>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>3050000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-16380000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>49945000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3625000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-12941000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>21513000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>73976000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>124000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>73852000</v>
+      </c>
       <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>-9107000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>470000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-220078000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-58968000</v>
+        <v>-118236000</v>
       </c>
       <c r="C3" t="n">
-        <v>-22555000</v>
+        <v>-366599000</v>
       </c>
       <c r="D3" t="n">
-        <v>30050000</v>
+        <v>13536000</v>
       </c>
       <c r="E3" t="n">
-        <v>-17000</v>
+        <v>-4966000</v>
       </c>
       <c r="F3" t="n">
-        <v>16109000</v>
+        <v>17929000</v>
       </c>
       <c r="G3" t="n">
-        <v>17929000</v>
+        <v>41947000</v>
       </c>
       <c r="H3" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-1818000</v>
+        <v>-24018000</v>
       </c>
       <c r="J3" t="n">
-        <v>50400000</v>
+        <v>-357999000</v>
       </c>
       <c r="K3" t="n">
-        <v>77915000</v>
+        <v>30000000</v>
       </c>
       <c r="L3" t="n">
-        <v>7495000</v>
+        <v>-353063000</v>
       </c>
       <c r="M3" t="n">
-        <v>-505000</v>
+        <v>-353303000</v>
       </c>
       <c r="N3" t="n">
-        <v>-505000</v>
+        <v>-357599000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4296000</v>
       </c>
       <c r="P3" t="n">
-        <v>7495000</v>
+        <v>240000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-22555000</v>
+        <v>-9000000</v>
       </c>
       <c r="R3" t="n">
-        <v>30050000</v>
+        <v>9240000</v>
       </c>
       <c r="S3" t="n">
-        <v>6733000</v>
+        <v>447251000</v>
       </c>
       <c r="T3" t="n">
-        <v>1717000</v>
+        <v>250000</v>
       </c>
       <c r="U3" t="n">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="V3" t="n">
-        <v>19227000</v>
+        <v>33527000</v>
       </c>
       <c r="W3" t="n">
-        <v>19227000</v>
+        <v>33527000</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-982000</v>
+        <v>431077000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>431077000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-982000</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>-17000</v>
+        <v>-4876000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-17000</v>
+        <v>-4966000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-58951000</v>
+        <v>-113270000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-640000</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-10134000</v>
+        <v>-32254000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3126000</v>
+        <v>34648000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-466000</v>
       </c>
       <c r="AL3" t="n">
-        <v>8355000</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-395000</v>
+        <v>11574000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-13757000</v>
+        <v>-3161000</v>
       </c>
       <c r="AO3" t="n">
-        <v>10030000</v>
+        <v>27246000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1107000</v>
+        <v>-545000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9280000</v>
+        <v>33610000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-12560000</v>
+        <v>-8000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>23643000</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+        <v>27615000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
       <c r="AU3" t="n">
-        <v>23643000</v>
+        <v>27615000</v>
       </c>
       <c r="AV3" t="n">
-        <v>260000</v>
+        <v>373000</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>-4602000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-102996000</v>
+        <v>-350031000</v>
       </c>
       <c r="AY3" t="n">
-        <v>54611000</v>
+        <v>164489000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-118236000</v>
+        <v>-58968000</v>
       </c>
       <c r="C4" t="n">
-        <v>-366599000</v>
+        <v>-22555000</v>
       </c>
       <c r="D4" t="n">
-        <v>13536000</v>
+        <v>30050000</v>
       </c>
       <c r="E4" t="n">
-        <v>-4966000</v>
+        <v>-17000</v>
       </c>
       <c r="F4" t="n">
+        <v>16109000</v>
+      </c>
+      <c r="G4" t="n">
         <v>17929000</v>
       </c>
-      <c r="G4" t="n">
-        <v>41947000</v>
-      </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="I4" t="n">
-        <v>-24018000</v>
+        <v>-1818000</v>
       </c>
       <c r="J4" t="n">
-        <v>-357999000</v>
+        <v>50400000</v>
       </c>
       <c r="K4" t="n">
-        <v>30000000</v>
+        <v>77915000</v>
       </c>
       <c r="L4" t="n">
-        <v>-353063000</v>
+        <v>7495000</v>
       </c>
       <c r="M4" t="n">
-        <v>-353303000</v>
+        <v>-505000</v>
       </c>
       <c r="N4" t="n">
-        <v>-357599000</v>
+        <v>-505000</v>
       </c>
       <c r="O4" t="n">
-        <v>4296000</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>240000</v>
+        <v>7495000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-9000000</v>
+        <v>-22555000</v>
       </c>
       <c r="R4" t="n">
-        <v>9240000</v>
+        <v>30050000</v>
       </c>
       <c r="S4" t="n">
-        <v>447251000</v>
+        <v>6733000</v>
       </c>
       <c r="T4" t="n">
-        <v>250000</v>
+        <v>1717000</v>
       </c>
       <c r="U4" t="n">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="V4" t="n">
-        <v>33527000</v>
+        <v>19227000</v>
       </c>
       <c r="W4" t="n">
-        <v>33527000</v>
+        <v>19227000</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>431077000</v>
+        <v>-982000</v>
       </c>
       <c r="Z4" t="n">
-        <v>431077000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-982000</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-4876000</v>
+        <v>-17000</v>
       </c>
       <c r="AE4" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-4966000</v>
+        <v>-17000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-113270000</v>
+        <v>-58951000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-640000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-32254000</v>
+        <v>-10134000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>34648000</v>
+        <v>3126000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-466000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>8355000</v>
       </c>
       <c r="AM4" t="n">
-        <v>11574000</v>
+        <v>-395000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-3161000</v>
+        <v>-13757000</v>
       </c>
       <c r="AO4" t="n">
-        <v>27246000</v>
+        <v>10030000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-545000</v>
+        <v>-1107000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>33610000</v>
+        <v>9280000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-8000000</v>
+        <v>-12560000</v>
       </c>
       <c r="AS4" t="n">
-        <v>27615000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
+        <v>23643000</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>27615000</v>
+        <v>23643000</v>
       </c>
       <c r="AV4" t="n">
-        <v>373000</v>
+        <v>260000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-4602000</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-350031000</v>
+        <v>-102996000</v>
       </c>
       <c r="AY4" t="n">
-        <v>164489000</v>
+        <v>54611000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-108417000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-92066000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>161857000</v>
-      </c>
+        <v>-64787000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>41947000</v>
+        <v>6448000</v>
       </c>
       <c r="G5" t="n">
-        <v>16748000</v>
+        <v>16109000</v>
       </c>
       <c r="H5" t="n">
-        <v>-733000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>25932000</v>
+        <v>-9661000</v>
       </c>
       <c r="J5" t="n">
-        <v>-10132000</v>
+        <v>56619000</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>69791000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-38772000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-38772000</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>69791000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-92066000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>161857000</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>144481000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>19723000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>11641000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>11641000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
+        <v>-1493000</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>113107000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>113107000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>-108417000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>210000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-35047000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>40240000</v>
-      </c>
+        <v>-64787000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
-        <v>3050000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-16380000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>49945000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3625000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-12941000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>21513000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>73976000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>124000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>73852000</v>
-      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="n">
-        <v>-9107000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>470000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-220078000</v>
-      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3686,192 +3686,192 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EN1" t="inlineStr">
@@ -3974,28 +3974,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.038</v>
+        <v>0.019</v>
       </c>
       <c r="V2" t="n">
-        <v>0.04</v>
+        <v>0.019</v>
       </c>
       <c r="W2" t="n">
-        <v>0.037</v>
+        <v>0.018</v>
       </c>
       <c r="X2" t="n">
-        <v>0.04</v>
+        <v>0.021</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.038</v>
+        <v>0.019</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.04</v>
+        <v>0.019</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.037</v>
+        <v>0.018</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.04</v>
+        <v>0.021</v>
       </c>
       <c r="AC2" t="n">
         <v>1473292800</v>
@@ -4007,31 +4007,31 @@
         <v>3.84</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.68</v>
+        <v>0.522</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>6452020</v>
+        <v>5268000</v>
       </c>
       <c r="AI2" t="n">
-        <v>6452020</v>
+        <v>5268000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14897645</v>
+        <v>14968326</v>
       </c>
       <c r="AK2" t="n">
-        <v>23063717</v>
+        <v>12940971</v>
       </c>
       <c r="AL2" t="n">
-        <v>23063717</v>
+        <v>12940971</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.037</v>
+        <v>0.02</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.038</v>
+        <v>0.021</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -4040,13 +4040,13 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>71245368</v>
+        <v>39372440</v>
       </c>
       <c r="AR2" t="n">
-        <v>71245366</v>
+        <v>35622683</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.037</v>
+        <v>0.018</v>
       </c>
       <c r="AT2" t="n">
         <v>0.159</v>
@@ -4055,16 +4055,16 @@
         <v>34.545452</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.038</v>
+        <v>0.019</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.4805659</v>
+        <v>0.81820744</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.06278</v>
+        <v>0.0518</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.085725</v>
+        <v>0.08054500000000001</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -4081,19 +4081,19 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>124827656</v>
+        <v>96262440</v>
       </c>
       <c r="BE2" t="n">
         <v>-2.4922</v>
       </c>
       <c r="BF2" t="n">
-        <v>1009074545</v>
+        <v>1078992104</v>
       </c>
       <c r="BG2" t="n">
         <v>1874878065</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.5892100300000001</v>
+        <v>0.54761004</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
@@ -4105,7 +4105,7 @@
         <v>0.048</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.7916666</v>
+        <v>0.4375</v>
       </c>
       <c r="BM2" t="n">
         <v>1751241600</v>
@@ -4137,16 +4137,16 @@
         <v>1727913600</v>
       </c>
       <c r="BV2" t="n">
-        <v>2.594</v>
+        <v>2</v>
       </c>
       <c r="BW2" t="n">
-        <v>-1.286</v>
+        <v>-0.992</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.6545454000000001</v>
+        <v>-0.8118812</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.016009</v>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="CC2" t="n">
-        <v>0.038</v>
+        <v>0.021</v>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
@@ -4250,143 +4250,143 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DB2" t="n">
-        <v>-0.024780001</v>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DC2" t="n">
-        <v>-0.3947117</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-0.047725003</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.5567221</v>
-      </c>
-      <c r="DF2" t="n">
+        <v>1782115692</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>finmb_8188399</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>BONJOUR HOLD</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>10.526319</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>Bonjour Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1058319000000</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.0020000003</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>0.018 - 0.021</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>14968326</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.0030000005</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.1666667</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>0.018 - 0.159</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.138</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.8679245</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-81.18812</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1740750508</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1740750508</v>
+      </c>
+      <c r="ED2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.030800002</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.5945946</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.059545003</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-0.73927623</v>
+      </c>
+      <c r="EK2" t="n">
         <v>15</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="EL2" t="n">
         <v>15</v>
       </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>finmb_8188399</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1058319000000</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>0.037 - 0.04</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>14897645</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0.0009999983000000001</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.027026981</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>0.037 - 0.159</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.12099999</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.7610062399999999</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-65.454544</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1740750508</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1740750508</v>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>BONJOUR HOLD</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>Bonjour Holdings Limited</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+      <c r="EM2" t="b">
+        <v>0</v>
       </c>
       <c r="EN2" t="inlineStr"/>
     </row>
